--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3333333333333333</v>
+        <v>0.3025210084033613</v>
       </c>
       <c r="B2">
-        <v>0.6666666666666666</v>
+        <v>0.1</v>
       </c>
       <c r="C2">
-        <v>0.5833333333333334</v>
+        <v>0.3381294964028777</v>
       </c>
       <c r="D2">
-        <v>0.5555555555555556</v>
+        <v>0.7131782945736435</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3025210084033613</v>
+        <v>0.2990654205607476</v>
       </c>
       <c r="B2">
-        <v>0.1</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="C2">
-        <v>0.3381294964028777</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="D2">
-        <v>0.7131782945736435</v>
+        <v>0.7</v>
       </c>
       <c r="E2">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
